--- a/managementreport/tests/fixtures/synthetic-pl.xlsx
+++ b/managementreport/tests/fixtures/synthetic-pl.xlsx
@@ -454,31 +454,31 @@
         <v>Account</v>
       </c>
       <c r="B6" t="str">
-        <v>Jan 2026</v>
+        <v>Sep 2026</v>
       </c>
       <c r="C6" t="str">
-        <v>Feb 2026</v>
+        <v>Aug 2026</v>
       </c>
       <c r="D6" t="str">
-        <v>Mar 2026</v>
+        <v>Jul 2026</v>
       </c>
       <c r="E6" t="str">
-        <v>Apr 2026</v>
+        <v>Jun 2026</v>
       </c>
       <c r="F6" t="str">
         <v>May 2026</v>
       </c>
       <c r="G6" t="str">
-        <v>Jun 2026</v>
+        <v>Apr 2026</v>
       </c>
       <c r="H6" t="str">
-        <v>Jul 2026</v>
+        <v>Mar 2026</v>
       </c>
       <c r="I6" t="str">
-        <v>Aug 2026</v>
+        <v>Feb 2026</v>
       </c>
       <c r="J6" t="str">
-        <v>Sep 2026</v>
+        <v>Jan 2026</v>
       </c>
       <c r="K6" t="str">
         <v>YTD</v>
@@ -494,31 +494,31 @@
         <v>Account Opening Fees</v>
       </c>
       <c r="B8">
+        <v>2500</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
+      </c>
+      <c r="D8">
+        <v>2000</v>
+      </c>
+      <c r="E8">
+        <v>1500</v>
+      </c>
+      <c r="F8">
+        <v>1500</v>
+      </c>
+      <c r="G8">
         <v>1000</v>
       </c>
-      <c r="C8">
+      <c r="H8">
         <v>1000</v>
       </c>
-      <c r="D8">
+      <c r="I8">
         <v>1000</v>
       </c>
-      <c r="E8">
+      <c r="J8">
         <v>1000</v>
-      </c>
-      <c r="F8">
-        <v>1500</v>
-      </c>
-      <c r="G8">
-        <v>1500</v>
-      </c>
-      <c r="H8">
-        <v>2000</v>
-      </c>
-      <c r="I8">
-        <v>2000</v>
-      </c>
-      <c r="J8">
-        <v>2500</v>
       </c>
       <c r="K8">
         <v>13500</v>
@@ -529,31 +529,31 @@
         <v>Subscription Fees</v>
       </c>
       <c r="B9">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="C9">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D9">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E9">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F9">
         <v>600</v>
       </c>
       <c r="G9">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H9">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I9">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J9">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="K9">
         <v>5400</v>
@@ -564,31 +564,31 @@
         <v>Transaction Fees</v>
       </c>
       <c r="B10">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="C10">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="D10">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E10">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="F10">
         <v>600</v>
       </c>
       <c r="G10">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="H10">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I10">
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="J10">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K10">
         <v>5400</v>
@@ -599,31 +599,31 @@
         <v>Total Trading Income</v>
       </c>
       <c r="B11">
-        <v>1900</v>
+        <v>4100</v>
       </c>
       <c r="C11">
-        <v>1950</v>
+        <v>3450</v>
       </c>
       <c r="D11">
-        <v>2000</v>
+        <v>3400</v>
       </c>
       <c r="E11">
-        <v>2050</v>
+        <v>2750</v>
       </c>
       <c r="F11">
         <v>2700</v>
       </c>
       <c r="G11">
-        <v>2750</v>
+        <v>2050</v>
       </c>
       <c r="H11">
-        <v>3400</v>
+        <v>2000</v>
       </c>
       <c r="I11">
-        <v>3450</v>
+        <v>1950</v>
       </c>
       <c r="J11">
-        <v>4100</v>
+        <v>1900</v>
       </c>
       <c r="K11">
         <v>24300</v>
@@ -779,31 +779,31 @@
         <v>EBITDA</v>
       </c>
       <c r="B17">
+        <v>2600</v>
+      </c>
+      <c r="C17">
+        <v>1950</v>
+      </c>
+      <c r="D17">
+        <v>1900</v>
+      </c>
+      <c r="E17">
+        <v>1250</v>
+      </c>
+      <c r="F17">
+        <v>1200</v>
+      </c>
+      <c r="G17">
+        <v>550</v>
+      </c>
+      <c r="H17">
+        <v>500</v>
+      </c>
+      <c r="I17">
+        <v>450</v>
+      </c>
+      <c r="J17">
         <v>400</v>
-      </c>
-      <c r="C17">
-        <v>450</v>
-      </c>
-      <c r="D17">
-        <v>500</v>
-      </c>
-      <c r="E17">
-        <v>550</v>
-      </c>
-      <c r="F17">
-        <v>1200</v>
-      </c>
-      <c r="G17">
-        <v>1250</v>
-      </c>
-      <c r="H17">
-        <v>1900</v>
-      </c>
-      <c r="I17">
-        <v>1950</v>
-      </c>
-      <c r="J17">
-        <v>2600</v>
       </c>
       <c r="K17">
         <v>10800</v>
